--- a/samples/예시_협력사_공정불량_RawData.xlsx
+++ b/samples/예시_협력사_공정불량_RawData.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:H154"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -409,6 +409,7 @@
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="34.83203125" customWidth="1"/>
     <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,28 +439,34 @@
       <c r="G3" t="str">
         <v>수량</v>
       </c>
+      <c r="H3" t="str">
+        <v>조치 내용</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="d">
-        <v>2026-01-06T00:00:00.000Z</v>
+        <v>2026-01-05T00:00:00.000Z</v>
       </c>
       <c r="C4" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D4" t="str">
-        <v>TP-1102</v>
+        <v>TP-5502</v>
       </c>
       <c r="E4" t="str">
-        <v>브래킷 ASSY</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F4" t="str">
-        <v>오품 납품 — 좌우 품번 바뀜</v>
+        <v>피팅부 오일 샘</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="H4" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="5">
@@ -467,22 +474,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="d">
-        <v>2026-01-09T00:00:00.000Z</v>
+        <v>2026-01-07T00:00:00.000Z</v>
       </c>
       <c r="C5" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D5" t="str">
-        <v>TP-3303</v>
+        <v>TP-3302</v>
       </c>
       <c r="E5" t="str">
-        <v>서포트</v>
+        <v>브래킷</v>
       </c>
       <c r="F5" t="str">
         <v>각장 부족</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -490,22 +497,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="d">
-        <v>2026-01-09T00:00:00.000Z</v>
+        <v>2026-01-08T00:00:00.000Z</v>
       </c>
       <c r="C6" t="str">
-        <v>협력사 F</v>
+        <v>협력사 B</v>
       </c>
       <c r="D6" t="str">
-        <v>TP-6602</v>
+        <v>TP-2201</v>
       </c>
       <c r="E6" t="str">
-        <v>스페이서</v>
+        <v>탱크</v>
       </c>
       <c r="F6" t="str">
-        <v>평면도 불량</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="7">
@@ -513,22 +523,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="d">
-        <v>2026-01-10T00:00:00.000Z</v>
+        <v>2026-01-09T00:00:00.000Z</v>
       </c>
       <c r="C7" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D7" t="str">
-        <v>TP-1103</v>
+        <v>TP-5503</v>
       </c>
       <c r="E7" t="str">
-        <v>커버</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F7" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>피팅부 오일 샘</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H7" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="8">
@@ -539,19 +552,22 @@
         <v>2026-01-10T00:00:00.000Z</v>
       </c>
       <c r="C8" t="str">
-        <v>협력사 E</v>
+        <v>협력사 D</v>
       </c>
       <c r="D8" t="str">
-        <v>TP-5501</v>
+        <v>TP-4403</v>
       </c>
       <c r="E8" t="str">
-        <v>유압 파이프</v>
+        <v>하우징</v>
       </c>
       <c r="F8" t="str">
-        <v>볼트 체결 토크 부족</v>
+        <v>탭 나사산 불량</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H8" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="9">
@@ -559,22 +575,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="d">
-        <v>2026-01-11T00:00:00.000Z</v>
+        <v>2026-01-14T00:00:00.000Z</v>
       </c>
       <c r="C9" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D9" t="str">
-        <v>TP-1101</v>
+        <v>TP-5501</v>
       </c>
       <c r="E9" t="str">
-        <v>브래킷</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F9" t="str">
-        <v>표면 찍힘</v>
+        <v>호스 클램프 미조임</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -582,22 +598,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="d">
-        <v>2026-01-16T00:00:00.000Z</v>
+        <v>2026-01-17T00:00:00.000Z</v>
       </c>
       <c r="C10" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D10" t="str">
-        <v>TP-5503</v>
+        <v>TP-2201</v>
       </c>
       <c r="E10" t="str">
-        <v>밸브 블록</v>
+        <v>탱크</v>
       </c>
       <c r="F10" t="str">
-        <v>와셔 누락</v>
+        <v>체결면 단차 발생</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H10" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="11">
@@ -605,22 +624,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="d">
-        <v>2026-01-18T00:00:00.000Z</v>
+        <v>2026-01-23T00:00:00.000Z</v>
       </c>
       <c r="C11" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D11" t="str">
-        <v>TP-4401</v>
+        <v>TP-1102</v>
       </c>
       <c r="E11" t="str">
-        <v>샤프트</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F11" t="str">
-        <v>탭 나사산 불량</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G11">
         <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="12">
@@ -628,22 +650,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
+        <v>2026-01-23T00:00:00.000Z</v>
       </c>
       <c r="C12" t="str">
-        <v>협력사 D</v>
+        <v>협력사 F</v>
       </c>
       <c r="D12" t="str">
-        <v>TP-4401</v>
+        <v>TP-6601</v>
       </c>
       <c r="E12" t="str">
-        <v>샤프트</v>
+        <v>가이드</v>
       </c>
       <c r="F12" t="str">
-        <v>탭 나사산 불량</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H12" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="13">
@@ -663,10 +688,13 @@
         <v>핀</v>
       </c>
       <c r="F13" t="str">
-        <v>이물 부착</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G13">
         <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="14">
@@ -674,22 +702,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="d">
-        <v>2026-02-01T00:00:00.000Z</v>
+        <v>2026-01-26T00:00:00.000Z</v>
       </c>
       <c r="C14" t="str">
-        <v>협력사 C</v>
+        <v>협력사 A</v>
       </c>
       <c r="D14" t="str">
-        <v>TP-3301</v>
+        <v>TP-1103</v>
       </c>
       <c r="E14" t="str">
-        <v>프레임</v>
+        <v>커버</v>
       </c>
       <c r="F14" t="str">
-        <v>용접 기공 다수</v>
+        <v>이종품 혼입 (타 품번 2개 섞임)</v>
       </c>
       <c r="G14">
         <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="15">
@@ -697,19 +728,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="d">
-        <v>2026-02-03T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C15" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D15" t="str">
-        <v>TP-1101</v>
+        <v>TP-2203</v>
       </c>
       <c r="E15" t="str">
-        <v>브래킷</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F15" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>압력 저하로 성능 미달</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -720,22 +751,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="d">
-        <v>2026-02-03T00:00:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C16" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D16" t="str">
-        <v>TP-3303</v>
+        <v>TP-5503</v>
       </c>
       <c r="E16" t="str">
-        <v>서포트</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F16" t="str">
-        <v>표면 찍힘</v>
+        <v>압력 저하로 성능 미달</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H16" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="17">
@@ -743,22 +777,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="d">
-        <v>2026-02-04T00:00:00.000Z</v>
+        <v>2026-02-03T00:00:00.000Z</v>
       </c>
       <c r="C17" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D17" t="str">
-        <v>TP-3303</v>
+        <v>TP-4405</v>
       </c>
       <c r="E17" t="str">
-        <v>서포트</v>
+        <v>플랜지</v>
       </c>
       <c r="F17" t="str">
-        <v>용접 기공 다수</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -766,22 +800,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="d">
-        <v>2026-02-07T00:00:00.000Z</v>
+        <v>2026-02-03T00:00:00.000Z</v>
       </c>
       <c r="C18" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D18" t="str">
-        <v>TP-1103</v>
+        <v>TP-5502</v>
       </c>
       <c r="E18" t="str">
-        <v>커버</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F18" t="str">
-        <v>라벨 오류로 품번 상이</v>
+        <v>압력 저하로 성능 미달</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="H18" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="19">
@@ -801,7 +838,7 @@
         <v>브래킷 ASSY</v>
       </c>
       <c r="F19" t="str">
-        <v>사양 상이 부품 혼입</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -815,19 +852,19 @@
         <v>2026-02-10T00:00:00.000Z</v>
       </c>
       <c r="C20" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D20" t="str">
-        <v>TP-2201</v>
+        <v>TP-3303</v>
       </c>
       <c r="E20" t="str">
-        <v>탱크</v>
+        <v>서포트</v>
       </c>
       <c r="F20" t="str">
-        <v>도장 박리</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -835,22 +872,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="d">
-        <v>2026-02-12T00:00:00.000Z</v>
+        <v>2026-02-11T00:00:00.000Z</v>
       </c>
       <c r="C21" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D21" t="str">
-        <v>TP-2201</v>
+        <v>TP-4402</v>
       </c>
       <c r="E21" t="str">
-        <v>탱크</v>
+        <v>부싱</v>
       </c>
       <c r="F21" t="str">
-        <v>보관 중 녹 발생</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="H21" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="22">
@@ -858,22 +898,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="d">
-        <v>2026-02-14T00:00:00.000Z</v>
+        <v>2026-02-13T00:00:00.000Z</v>
       </c>
       <c r="C22" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D22" t="str">
-        <v>TP-3303</v>
+        <v>TP-3301</v>
       </c>
       <c r="E22" t="str">
-        <v>서포트</v>
+        <v>프레임</v>
       </c>
       <c r="F22" t="str">
-        <v>미용접 구간 있음</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -881,22 +921,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="d">
-        <v>2026-02-17T00:00:00.000Z</v>
+        <v>2026-02-14T00:00:00.000Z</v>
       </c>
       <c r="C23" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D23" t="str">
-        <v>TP-1102</v>
+        <v>TP-5501</v>
       </c>
       <c r="E23" t="str">
-        <v>브래킷 ASSY</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F23" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>기밀 시험 리크 발생</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -904,22 +944,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="d">
-        <v>2026-02-19T00:00:00.000Z</v>
+        <v>2026-02-16T00:00:00.000Z</v>
       </c>
       <c r="C24" t="str">
-        <v>협력사 E</v>
+        <v>협력사 F</v>
       </c>
       <c r="D24" t="str">
-        <v>TP-5503</v>
+        <v>TP-6602</v>
       </c>
       <c r="E24" t="str">
-        <v>밸브 블록</v>
+        <v>스페이서</v>
       </c>
       <c r="F24" t="str">
-        <v>이물 부착</v>
+        <v>보관 중 녹 발생</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="H24" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="25">
@@ -927,22 +970,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="d">
-        <v>2026-02-21T00:00:00.000Z</v>
+        <v>2026-02-17T00:00:00.000Z</v>
       </c>
       <c r="C25" t="str">
-        <v>협력사 B</v>
+        <v>협력사 A</v>
       </c>
       <c r="D25" t="str">
-        <v>TP-2203</v>
+        <v>TP-1102</v>
       </c>
       <c r="E25" t="str">
-        <v>도어 판넬</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F25" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>이종품 혼입 (타 품번 2개 섞임)</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H25" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="26">
@@ -950,22 +996,22 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="d">
-        <v>2026-02-24T00:00:00.000Z</v>
+        <v>2026-02-18T00:00:00.000Z</v>
       </c>
       <c r="C26" t="str">
         <v>협력사 A</v>
       </c>
       <c r="D26" t="str">
-        <v>TP-1104</v>
+        <v>TP-1102</v>
       </c>
       <c r="E26" t="str">
-        <v>핀</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F26" t="str">
-        <v>이종 볼트 혼용</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -973,22 +1019,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="d">
-        <v>2026-02-26T00:00:00.000Z</v>
+        <v>2026-02-20T00:00:00.000Z</v>
       </c>
       <c r="C27" t="str">
-        <v>협력사 E</v>
+        <v>협력사 D</v>
       </c>
       <c r="D27" t="str">
-        <v>TP-5501</v>
+        <v>TP-4403</v>
       </c>
       <c r="E27" t="str">
-        <v>유압 파이프</v>
+        <v>하우징</v>
       </c>
       <c r="F27" t="str">
-        <v>와셔 누락</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H27" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="28">
@@ -996,22 +1045,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="d">
-        <v>2026-02-27T00:00:00.000Z</v>
+        <v>2026-02-21T00:00:00.000Z</v>
       </c>
       <c r="C28" t="str">
-        <v>협력사 C</v>
+        <v>협력사 B</v>
       </c>
       <c r="D28" t="str">
-        <v>TP-3303</v>
+        <v>TP-2203</v>
       </c>
       <c r="E28" t="str">
-        <v>서포트</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F28" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H28" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="29">
@@ -1019,22 +1071,25 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="d">
-        <v>2026-02-28T00:00:00.000Z</v>
+        <v>2026-02-22T00:00:00.000Z</v>
       </c>
       <c r="C29" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D29" t="str">
-        <v>TP-4402</v>
+        <v>TP-1101</v>
       </c>
       <c r="E29" t="str">
-        <v>부싱</v>
+        <v>브래킷</v>
       </c>
       <c r="F29" t="str">
-        <v>탭 나사산 불량</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H29" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="30">
@@ -1042,22 +1097,22 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="d">
-        <v>2026-03-01T00:00:00.000Z</v>
+        <v>2026-02-23T00:00:00.000Z</v>
       </c>
       <c r="C30" t="str">
         <v>협력사 B</v>
       </c>
       <c r="D30" t="str">
-        <v>TP-2202</v>
+        <v>TP-2203</v>
       </c>
       <c r="E30" t="str">
-        <v>커버</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F30" t="str">
-        <v>도장 흐름 발생</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1065,22 +1120,22 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="d">
-        <v>2026-03-04T00:00:00.000Z</v>
+        <v>2026-02-28T00:00:00.000Z</v>
       </c>
       <c r="C31" t="str">
-        <v>협력사 D</v>
+        <v>협력사 B</v>
       </c>
       <c r="D31" t="str">
-        <v>TP-4401</v>
+        <v>TP-2203</v>
       </c>
       <c r="E31" t="str">
-        <v>샤프트</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F31" t="str">
-        <v>평면도 불량</v>
+        <v>압력 저하로 성능 미달</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1088,22 +1143,25 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="d">
-        <v>2026-03-04T00:00:00.000Z</v>
+        <v>2026-03-01T00:00:00.000Z</v>
       </c>
       <c r="C32" t="str">
-        <v>협력사 D</v>
+        <v>협력사 B</v>
       </c>
       <c r="D32" t="str">
-        <v>TP-4402</v>
+        <v>TP-2202</v>
       </c>
       <c r="E32" t="str">
-        <v>부싱</v>
+        <v>커버</v>
       </c>
       <c r="F32" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="H32" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="33">
@@ -1111,22 +1169,25 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="d">
-        <v>2026-03-07T00:00:00.000Z</v>
+        <v>2026-03-01T00:00:00.000Z</v>
       </c>
       <c r="C33" t="str">
-        <v>협력사 D</v>
+        <v>협력사 B</v>
       </c>
       <c r="D33" t="str">
-        <v>TP-4405</v>
+        <v>TP-2201</v>
       </c>
       <c r="E33" t="str">
-        <v>플랜지</v>
+        <v>탱크</v>
       </c>
       <c r="F33" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>체결면 단차 발생</v>
       </c>
       <c r="G33">
         <v>2</v>
+      </c>
+      <c r="H33" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="34">
@@ -1134,7 +1195,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="d">
-        <v>2026-03-08T00:00:00.000Z</v>
+        <v>2026-03-01T00:00:00.000Z</v>
       </c>
       <c r="C34" t="str">
         <v>협력사 B</v>
@@ -1146,10 +1207,10 @@
         <v>커버</v>
       </c>
       <c r="F34" t="str">
-        <v>도막 두께 부족</v>
+        <v>보관 중 녹 발생</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1157,22 +1218,25 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="d">
-        <v>2026-03-09T00:00:00.000Z</v>
+        <v>2026-03-03T00:00:00.000Z</v>
       </c>
       <c r="C35" t="str">
         <v>협력사 B</v>
       </c>
       <c r="D35" t="str">
-        <v>TP-2203</v>
+        <v>TP-2202</v>
       </c>
       <c r="E35" t="str">
-        <v>도어 판넬</v>
+        <v>커버</v>
       </c>
       <c r="F35" t="str">
-        <v>도장 박리</v>
+        <v>작동 시 소음 발생</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="H35" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="36">
@@ -1180,22 +1244,22 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="d">
-        <v>2026-03-11T00:00:00.000Z</v>
+        <v>2026-03-04T00:00:00.000Z</v>
       </c>
       <c r="C36" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D36" t="str">
-        <v>TP-1101</v>
+        <v>TP-2202</v>
       </c>
       <c r="E36" t="str">
-        <v>브래킷</v>
+        <v>커버</v>
       </c>
       <c r="F36" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1203,22 +1267,25 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="d">
-        <v>2026-03-11T00:00:00.000Z</v>
+        <v>2026-03-06T00:00:00.000Z</v>
       </c>
       <c r="C37" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D37" t="str">
-        <v>TP-3303</v>
+        <v>TP-4401</v>
       </c>
       <c r="E37" t="str">
-        <v>서포트</v>
+        <v>샤프트</v>
       </c>
       <c r="F37" t="str">
-        <v>미용접 구간 있음</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G37">
         <v>4</v>
+      </c>
+      <c r="H37" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="38">
@@ -1226,22 +1293,25 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="d">
-        <v>2026-03-11T00:00:00.000Z</v>
+        <v>2026-03-07T00:00:00.000Z</v>
       </c>
       <c r="C38" t="str">
-        <v>협력사 C</v>
+        <v>협력사 A</v>
       </c>
       <c r="D38" t="str">
-        <v>TP-3302</v>
+        <v>TP-1102</v>
       </c>
       <c r="E38" t="str">
-        <v>브래킷</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F38" t="str">
-        <v>용접부 균열 발생</v>
+        <v>와셔 누락</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H38" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="39">
@@ -1249,22 +1319,25 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="d">
-        <v>2026-03-11T00:00:00.000Z</v>
+        <v>2026-03-07T00:00:00.000Z</v>
       </c>
       <c r="C39" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D39" t="str">
-        <v>TP-5501</v>
+        <v>TP-1103</v>
       </c>
       <c r="E39" t="str">
-        <v>유압 파이프</v>
+        <v>커버</v>
       </c>
       <c r="F39" t="str">
-        <v>와셔 누락</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H39" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="40">
@@ -1272,22 +1345,25 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="d">
-        <v>2026-03-17T00:00:00.000Z</v>
+        <v>2026-03-07T00:00:00.000Z</v>
       </c>
       <c r="C40" t="str">
         <v>협력사 A</v>
       </c>
       <c r="D40" t="str">
-        <v>TP-1101</v>
+        <v>TP-1104</v>
       </c>
       <c r="E40" t="str">
-        <v>브래킷</v>
+        <v>핀</v>
       </c>
       <c r="F40" t="str">
-        <v>표면 찍힘</v>
+        <v>와셔 누락</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H40" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="41">
@@ -1295,22 +1371,22 @@
         <v>38</v>
       </c>
       <c r="B41" s="1" t="d">
-        <v>2026-03-19T00:00:00.000Z</v>
+        <v>2026-03-09T00:00:00.000Z</v>
       </c>
       <c r="C41" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D41" t="str">
-        <v>TP-1102</v>
+        <v>TP-2203</v>
       </c>
       <c r="E41" t="str">
-        <v>브래킷 ASSY</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F41" t="str">
-        <v>표면 찍힘</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1318,22 +1394,25 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="d">
-        <v>2026-03-21T00:00:00.000Z</v>
+        <v>2026-03-09T00:00:00.000Z</v>
       </c>
       <c r="C42" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D42" t="str">
-        <v>TP-4403</v>
+        <v>TP-4402</v>
       </c>
       <c r="E42" t="str">
-        <v>하우징</v>
+        <v>부싱</v>
       </c>
       <c r="F42" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H42" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="43">
@@ -1341,22 +1420,22 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="d">
-        <v>2026-03-22T00:00:00.000Z</v>
+        <v>2026-03-09T00:00:00.000Z</v>
       </c>
       <c r="C43" t="str">
-        <v>협력사 D</v>
+        <v>협력사 E</v>
       </c>
       <c r="D43" t="str">
-        <v>TP-4402</v>
+        <v>TP-5502</v>
       </c>
       <c r="E43" t="str">
-        <v>부싱</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F43" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>기밀 시험 리크 발생</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1364,22 +1443,25 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="d">
-        <v>2026-03-22T00:00:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C44" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D44" t="str">
-        <v>TP-5501</v>
+        <v>TP-1101</v>
       </c>
       <c r="E44" t="str">
-        <v>유압 파이프</v>
+        <v>브래킷</v>
       </c>
       <c r="F44" t="str">
-        <v>유압 파이프 연결부 누유</v>
+        <v>이종품 혼입 (타 품번 2개 섞임)</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H44" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="45">
@@ -1387,22 +1469,25 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="d">
-        <v>2026-03-25T00:00:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C45" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D45" t="str">
-        <v>TP-4403</v>
+        <v>TP-1103</v>
       </c>
       <c r="E45" t="str">
-        <v>하우징</v>
+        <v>커버</v>
       </c>
       <c r="F45" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H45" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="46">
@@ -1410,7 +1495,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="d">
-        <v>2026-03-26T00:00:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C46" t="str">
         <v>협력사 B</v>
@@ -1422,7 +1507,7 @@
         <v>도어 판넬</v>
       </c>
       <c r="F46" t="str">
-        <v>도장면 기포</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -1433,22 +1518,25 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="d">
-        <v>2026-03-26T00:00:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C47" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D47" t="str">
-        <v>TP-2203</v>
+        <v>TP-3302</v>
       </c>
       <c r="E47" t="str">
-        <v>도어 판넬</v>
+        <v>브래킷</v>
       </c>
       <c r="F47" t="str">
-        <v>도장 박리</v>
+        <v>용접부 균열 발생</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H47" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="48">
@@ -1456,22 +1544,25 @@
         <v>45</v>
       </c>
       <c r="B48" s="1" t="d">
-        <v>2026-03-26T00:00:00.000Z</v>
+        <v>2026-03-14T00:00:00.000Z</v>
       </c>
       <c r="C48" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D48" t="str">
-        <v>TP-5501</v>
+        <v>TP-1101</v>
       </c>
       <c r="E48" t="str">
-        <v>유압 파이프</v>
+        <v>브래킷</v>
       </c>
       <c r="F48" t="str">
-        <v>오조립(방향 반대)</v>
+        <v>라벨 오류로 품번 상이</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H48" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="49">
@@ -1479,22 +1570,25 @@
         <v>46</v>
       </c>
       <c r="B49" s="1" t="d">
-        <v>2026-03-29T00:00:00.000Z</v>
+        <v>2026-03-15T00:00:00.000Z</v>
       </c>
       <c r="C49" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D49" t="str">
-        <v>TP-3303</v>
+        <v>TP-5502</v>
       </c>
       <c r="E49" t="str">
-        <v>서포트</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F49" t="str">
-        <v>미용접 구간 있음</v>
+        <v>밸브 작동 불량</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H49" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="50">
@@ -1502,22 +1596,25 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="d">
-        <v>2026-03-30T00:00:00.000Z</v>
+        <v>2026-03-21T00:00:00.000Z</v>
       </c>
       <c r="C50" t="str">
         <v>협력사 A</v>
       </c>
       <c r="D50" t="str">
-        <v>TP-1102</v>
+        <v>TP-1104</v>
       </c>
       <c r="E50" t="str">
-        <v>브래킷 ASSY</v>
+        <v>핀</v>
       </c>
       <c r="F50" t="str">
-        <v>오품 납품 — 좌우 품번 바뀜</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H50" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="51">
@@ -1525,22 +1622,22 @@
         <v>48</v>
       </c>
       <c r="B51" s="1" t="d">
-        <v>2026-03-31T00:00:00.000Z</v>
+        <v>2026-03-24T00:00:00.000Z</v>
       </c>
       <c r="C51" t="str">
-        <v>협력사 D</v>
+        <v>협력사 C</v>
       </c>
       <c r="D51" t="str">
-        <v>TP-4401</v>
+        <v>TP-3302</v>
       </c>
       <c r="E51" t="str">
-        <v>샤프트</v>
+        <v>브래킷</v>
       </c>
       <c r="F51" t="str">
-        <v>탭 나사산 불량</v>
+        <v>평면도 불량</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -1548,19 +1645,19 @@
         <v>49</v>
       </c>
       <c r="B52" s="1" t="d">
-        <v>2026-04-01T00:00:00.000Z</v>
+        <v>2026-03-24T00:00:00.000Z</v>
       </c>
       <c r="C52" t="str">
         <v>협력사 E</v>
       </c>
       <c r="D52" t="str">
-        <v>TP-5501</v>
+        <v>TP-5503</v>
       </c>
       <c r="E52" t="str">
-        <v>유압 파이프</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F52" t="str">
-        <v>이물 부착</v>
+        <v>너트 풀림</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -1571,22 +1668,22 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="d">
-        <v>2026-04-03T00:00:00.000Z</v>
+        <v>2026-03-25T00:00:00.000Z</v>
       </c>
       <c r="C53" t="str">
-        <v>협력사 D</v>
+        <v>협력사 C</v>
       </c>
       <c r="D53" t="str">
-        <v>TP-4402</v>
+        <v>TP-3303</v>
       </c>
       <c r="E53" t="str">
-        <v>부싱</v>
+        <v>서포트</v>
       </c>
       <c r="F53" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1594,22 +1691,25 @@
         <v>51</v>
       </c>
       <c r="B54" s="1" t="d">
-        <v>2026-04-04T00:00:00.000Z</v>
+        <v>2026-03-26T00:00:00.000Z</v>
       </c>
       <c r="C54" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D54" t="str">
-        <v>TP-3302</v>
+        <v>TP-4402</v>
       </c>
       <c r="E54" t="str">
-        <v>브래킷</v>
+        <v>부싱</v>
       </c>
       <c r="F54" t="str">
-        <v>언더컷 발생</v>
+        <v>평면도 불량</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H54" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="55">
@@ -1617,22 +1717,25 @@
         <v>52</v>
       </c>
       <c r="B55" s="1" t="d">
-        <v>2026-04-05T00:00:00.000Z</v>
+        <v>2026-03-29T00:00:00.000Z</v>
       </c>
       <c r="C55" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D55" t="str">
-        <v>TP-1103</v>
+        <v>TP-2203</v>
       </c>
       <c r="E55" t="str">
-        <v>커버</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F55" t="str">
-        <v>표면 찍힘</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H55" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="56">
@@ -1640,22 +1743,25 @@
         <v>53</v>
       </c>
       <c r="B56" s="1" t="d">
-        <v>2026-04-05T00:00:00.000Z</v>
+        <v>2026-03-30T00:00:00.000Z</v>
       </c>
       <c r="C56" t="str">
-        <v>협력사 F</v>
+        <v>협력사 D</v>
       </c>
       <c r="D56" t="str">
-        <v>TP-6601</v>
+        <v>TP-4401</v>
       </c>
       <c r="E56" t="str">
-        <v>가이드</v>
+        <v>샤프트</v>
       </c>
       <c r="F56" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H56" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="57">
@@ -1666,19 +1772,22 @@
         <v>2026-04-06T00:00:00.000Z</v>
       </c>
       <c r="C57" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D57" t="str">
-        <v>TP-1104</v>
+        <v>TP-2201</v>
       </c>
       <c r="E57" t="str">
-        <v>핀</v>
+        <v>탱크</v>
       </c>
       <c r="F57" t="str">
-        <v>탭 나사산 불량</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H57" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="58">
@@ -1689,19 +1798,19 @@
         <v>2026-04-06T00:00:00.000Z</v>
       </c>
       <c r="C58" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D58" t="str">
-        <v>TP-2201</v>
+        <v>TP-4405</v>
       </c>
       <c r="E58" t="str">
-        <v>탱크</v>
+        <v>플랜지</v>
       </c>
       <c r="F58" t="str">
-        <v>도장 박리</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1709,19 +1818,19 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="d">
-        <v>2026-04-06T00:00:00.000Z</v>
+        <v>2026-04-10T00:00:00.000Z</v>
       </c>
       <c r="C59" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D59" t="str">
-        <v>TP-4405</v>
+        <v>TP-1102</v>
       </c>
       <c r="E59" t="str">
-        <v>플랜지</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F59" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -1732,7 +1841,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="1" t="d">
-        <v>2026-04-09T00:00:00.000Z</v>
+        <v>2026-04-11T00:00:00.000Z</v>
       </c>
       <c r="C60" t="str">
         <v>협력사 B</v>
@@ -1744,10 +1853,13 @@
         <v>도어 판넬</v>
       </c>
       <c r="F60" t="str">
-        <v>도막 두께 부족</v>
+        <v>보관 중 녹 발생</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H60" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="61">
@@ -1755,22 +1867,25 @@
         <v>58</v>
       </c>
       <c r="B61" s="1" t="d">
-        <v>2026-04-16T00:00:00.000Z</v>
+        <v>2026-04-12T00:00:00.000Z</v>
       </c>
       <c r="C61" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D61" t="str">
-        <v>TP-5502</v>
+        <v>TP-1103</v>
       </c>
       <c r="E61" t="str">
-        <v>호스 ASSY</v>
+        <v>커버</v>
       </c>
       <c r="F61" t="str">
-        <v>와셔 누락</v>
+        <v>호스 클램프 미조임</v>
       </c>
       <c r="G61">
         <v>2</v>
+      </c>
+      <c r="H61" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="62">
@@ -1778,19 +1893,19 @@
         <v>59</v>
       </c>
       <c r="B62" s="1" t="d">
-        <v>2026-04-18T00:00:00.000Z</v>
+        <v>2026-04-13T00:00:00.000Z</v>
       </c>
       <c r="C62" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D62" t="str">
-        <v>TP-2203</v>
+        <v>TP-3302</v>
       </c>
       <c r="E62" t="str">
-        <v>도어 판넬</v>
+        <v>브래킷</v>
       </c>
       <c r="F62" t="str">
-        <v>이물 부착</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G62">
         <v>4</v>
@@ -1801,22 +1916,25 @@
         <v>60</v>
       </c>
       <c r="B63" s="1" t="d">
-        <v>2026-04-24T00:00:00.000Z</v>
+        <v>2026-04-13T00:00:00.000Z</v>
       </c>
       <c r="C63" t="str">
         <v>협력사 E</v>
       </c>
       <c r="D63" t="str">
-        <v>TP-5501</v>
+        <v>TP-5503</v>
       </c>
       <c r="E63" t="str">
-        <v>유압 파이프</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F63" t="str">
-        <v>피팅부 오일 샘</v>
+        <v>볼트 체결 토크 부족</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="H63" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="64">
@@ -1824,22 +1942,22 @@
         <v>61</v>
       </c>
       <c r="B64" s="1" t="d">
-        <v>2026-04-27T00:00:00.000Z</v>
+        <v>2026-04-14T00:00:00.000Z</v>
       </c>
       <c r="C64" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D64" t="str">
-        <v>TP-4405</v>
+        <v>TP-4402</v>
       </c>
       <c r="E64" t="str">
-        <v>플랜지</v>
+        <v>부싱</v>
       </c>
       <c r="F64" t="str">
-        <v>평면도 불량</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1847,22 +1965,22 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="d">
-        <v>2026-05-01T00:00:00.000Z</v>
+        <v>2026-04-15T00:00:00.000Z</v>
       </c>
       <c r="C65" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D65" t="str">
-        <v>TP-4405</v>
+        <v>TP-1102</v>
       </c>
       <c r="E65" t="str">
-        <v>플랜지</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F65" t="str">
-        <v>표면 찍힘</v>
+        <v>와셔 누락</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -1870,22 +1988,25 @@
         <v>63</v>
       </c>
       <c r="B66" s="1" t="d">
-        <v>2026-05-01T00:00:00.000Z</v>
+        <v>2026-04-18T00:00:00.000Z</v>
       </c>
       <c r="C66" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D66" t="str">
-        <v>TP-5501</v>
+        <v>TP-1103</v>
       </c>
       <c r="E66" t="str">
-        <v>유압 파이프</v>
+        <v>커버</v>
       </c>
       <c r="F66" t="str">
-        <v>볼트 체결 토크 부족</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H66" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="67">
@@ -1893,22 +2014,25 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="d">
-        <v>2026-05-02T00:00:00.000Z</v>
+        <v>2026-04-19T00:00:00.000Z</v>
       </c>
       <c r="C67" t="str">
-        <v>협력사 C</v>
+        <v>협력사 B</v>
       </c>
       <c r="D67" t="str">
-        <v>TP-3301</v>
+        <v>TP-2203</v>
       </c>
       <c r="E67" t="str">
-        <v>프레임</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F67" t="str">
-        <v>용접 기공 다수</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H67" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="68">
@@ -1916,22 +2040,25 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="d">
-        <v>2026-05-04T00:00:00.000Z</v>
+        <v>2026-04-21T00:00:00.000Z</v>
       </c>
       <c r="C68" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D68" t="str">
-        <v>TP-3301</v>
+        <v>TP-3302</v>
       </c>
       <c r="E68" t="str">
-        <v>프레임</v>
+        <v>브래킷</v>
       </c>
       <c r="F68" t="str">
-        <v>용접 기공 다수</v>
+        <v>언더컷 발생</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H68" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="69">
@@ -1939,22 +2066,22 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="d">
-        <v>2026-05-07T00:00:00.000Z</v>
+        <v>2026-04-21T00:00:00.000Z</v>
       </c>
       <c r="C69" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D69" t="str">
-        <v>TP-2202</v>
+        <v>TP-4402</v>
       </c>
       <c r="E69" t="str">
-        <v>커버</v>
+        <v>부싱</v>
       </c>
       <c r="F69" t="str">
-        <v>도장 흐름 발생</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -1962,22 +2089,25 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="d">
-        <v>2026-05-07T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C70" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D70" t="str">
-        <v>TP-2201</v>
+        <v>TP-3303</v>
       </c>
       <c r="E70" t="str">
-        <v>탱크</v>
+        <v>서포트</v>
       </c>
       <c r="F70" t="str">
-        <v>도막 두께 부족</v>
+        <v>평면도 불량</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H70" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="71">
@@ -1985,22 +2115,25 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="d">
-        <v>2026-05-08T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C71" t="str">
-        <v>협력사 D</v>
+        <v>협력사 E</v>
       </c>
       <c r="D71" t="str">
-        <v>TP-4402</v>
+        <v>TP-5501</v>
       </c>
       <c r="E71" t="str">
-        <v>부싱</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F71" t="str">
-        <v>평면도 불량</v>
+        <v>볼트 체결 토크 부족</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H71" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="72">
@@ -2008,22 +2141,25 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="d">
-        <v>2026-05-10T00:00:00.000Z</v>
+        <v>2026-04-22T00:00:00.000Z</v>
       </c>
       <c r="C72" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D72" t="str">
-        <v>TP-3302</v>
+        <v>TP-5503</v>
       </c>
       <c r="E72" t="str">
-        <v>브래킷</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F72" t="str">
-        <v>각장 부족</v>
+        <v>유압 파이프 연결부 누유</v>
       </c>
       <c r="G72">
         <v>5</v>
+      </c>
+      <c r="H72" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="73">
@@ -2031,22 +2167,25 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="d">
-        <v>2026-05-12T00:00:00.000Z</v>
+        <v>2026-04-25T00:00:00.000Z</v>
       </c>
       <c r="C73" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D73" t="str">
-        <v>TP-1102</v>
+        <v>TP-3302</v>
       </c>
       <c r="E73" t="str">
-        <v>브래킷 ASSY</v>
+        <v>브래킷</v>
       </c>
       <c r="F73" t="str">
-        <v>오품 납품 — 좌우 품번 바뀜</v>
+        <v>브래킷 정렬 틀어짐</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="H73" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="74">
@@ -2054,22 +2193,25 @@
         <v>71</v>
       </c>
       <c r="B74" s="1" t="d">
-        <v>2026-05-12T00:00:00.000Z</v>
+        <v>2026-04-26T00:00:00.000Z</v>
       </c>
       <c r="C74" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D74" t="str">
-        <v>TP-5502</v>
+        <v>TP-2201</v>
       </c>
       <c r="E74" t="str">
-        <v>호스 ASSY</v>
+        <v>탱크</v>
       </c>
       <c r="F74" t="str">
-        <v>이물 부착</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G74">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="H74" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="75">
@@ -2077,22 +2219,22 @@
         <v>72</v>
       </c>
       <c r="B75" s="1" t="d">
-        <v>2026-05-13T00:00:00.000Z</v>
+        <v>2026-04-27T00:00:00.000Z</v>
       </c>
       <c r="C75" t="str">
-        <v>협력사 A</v>
+        <v>협력사 D</v>
       </c>
       <c r="D75" t="str">
-        <v>TP-1104</v>
+        <v>TP-4403</v>
       </c>
       <c r="E75" t="str">
-        <v>핀</v>
+        <v>하우징</v>
       </c>
       <c r="F75" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -2100,22 +2242,25 @@
         <v>73</v>
       </c>
       <c r="B76" s="1" t="d">
-        <v>2026-05-18T00:00:00.000Z</v>
+        <v>2026-04-28T00:00:00.000Z</v>
       </c>
       <c r="C76" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D76" t="str">
-        <v>TP-2201</v>
+        <v>TP-4401</v>
       </c>
       <c r="E76" t="str">
-        <v>탱크</v>
+        <v>샤프트</v>
       </c>
       <c r="F76" t="str">
-        <v>도금면 부식</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H76" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="77">
@@ -2123,22 +2268,25 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="d">
-        <v>2026-05-20T00:00:00.000Z</v>
+        <v>2026-04-30T00:00:00.000Z</v>
       </c>
       <c r="C77" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D77" t="str">
-        <v>TP-1103</v>
+        <v>TP-5502</v>
       </c>
       <c r="E77" t="str">
-        <v>커버</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F77" t="str">
-        <v>오조립(방향 반대)</v>
+        <v>작동 시 소음 발생</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H77" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="78">
@@ -2146,22 +2294,25 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="d">
-        <v>2026-05-20T00:00:00.000Z</v>
+        <v>2026-05-01T00:00:00.000Z</v>
       </c>
       <c r="C78" t="str">
-        <v>협력사 B</v>
+        <v>협력사 E</v>
       </c>
       <c r="D78" t="str">
-        <v>TP-2202</v>
+        <v>TP-5503</v>
       </c>
       <c r="E78" t="str">
-        <v>커버</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F78" t="str">
-        <v>검사성적서 미첨부</v>
+        <v>피팅부 오일 샘</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H78" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="79">
@@ -2169,22 +2320,25 @@
         <v>76</v>
       </c>
       <c r="B79" s="1" t="d">
-        <v>2026-05-22T00:00:00.000Z</v>
+        <v>2026-05-03T00:00:00.000Z</v>
       </c>
       <c r="C79" t="str">
-        <v>협력사 A</v>
+        <v>협력사 E</v>
       </c>
       <c r="D79" t="str">
-        <v>TP-1103</v>
+        <v>TP-5502</v>
       </c>
       <c r="E79" t="str">
-        <v>커버</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F79" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>유압 파이프 연결부 누유</v>
       </c>
       <c r="G79">
         <v>2</v>
+      </c>
+      <c r="H79" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="80">
@@ -2192,22 +2346,25 @@
         <v>77</v>
       </c>
       <c r="B80" s="1" t="d">
-        <v>2026-05-24T00:00:00.000Z</v>
+        <v>2026-05-06T00:00:00.000Z</v>
       </c>
       <c r="C80" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D80" t="str">
-        <v>TP-3303</v>
+        <v>TP-4402</v>
       </c>
       <c r="E80" t="str">
-        <v>서포트</v>
+        <v>부싱</v>
       </c>
       <c r="F80" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G80">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H80" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="81">
@@ -2215,22 +2372,25 @@
         <v>78</v>
       </c>
       <c r="B81" s="1" t="d">
-        <v>2026-05-25T00:00:00.000Z</v>
+        <v>2026-05-07T00:00:00.000Z</v>
       </c>
       <c r="C81" t="str">
         <v>협력사 E</v>
       </c>
       <c r="D81" t="str">
-        <v>TP-5501</v>
+        <v>TP-5503</v>
       </c>
       <c r="E81" t="str">
-        <v>유압 파이프</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F81" t="str">
-        <v>기밀 시험 리크 발생</v>
+        <v>유압 파이프 연결부 누유</v>
       </c>
       <c r="G81">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H81" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="82">
@@ -2238,19 +2398,19 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-10T00:00:00.000Z</v>
       </c>
       <c r="C82" t="str">
-        <v>협력사 D</v>
+        <v>협력사 B</v>
       </c>
       <c r="D82" t="str">
-        <v>TP-4405</v>
+        <v>TP-2201</v>
       </c>
       <c r="E82" t="str">
-        <v>플랜지</v>
+        <v>탱크</v>
       </c>
       <c r="F82" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -2261,22 +2421,25 @@
         <v>80</v>
       </c>
       <c r="B83" s="1" t="d">
-        <v>2026-05-29T00:00:00.000Z</v>
+        <v>2026-05-10T00:00:00.000Z</v>
       </c>
       <c r="C83" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D83" t="str">
-        <v>TP-4405</v>
+        <v>TP-4401</v>
       </c>
       <c r="E83" t="str">
-        <v>플랜지</v>
+        <v>샤프트</v>
       </c>
       <c r="F83" t="str">
-        <v>보관 중 녹 발생</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H83" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="84">
@@ -2284,22 +2447,25 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="d">
-        <v>2026-05-30T00:00:00.000Z</v>
+        <v>2026-05-12T00:00:00.000Z</v>
       </c>
       <c r="C84" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D84" t="str">
-        <v>TP-4405</v>
+        <v>TP-1102</v>
       </c>
       <c r="E84" t="str">
-        <v>플랜지</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F84" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>오품 납품 — 좌우 품번 바뀜</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H84" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="85">
@@ -2307,22 +2473,25 @@
         <v>82</v>
       </c>
       <c r="B85" s="1" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-13T00:00:00.000Z</v>
       </c>
       <c r="C85" t="str">
         <v>협력사 B</v>
       </c>
       <c r="D85" t="str">
-        <v>TP-2202</v>
+        <v>TP-2201</v>
       </c>
       <c r="E85" t="str">
-        <v>커버</v>
+        <v>탱크</v>
       </c>
       <c r="F85" t="str">
-        <v>도장 박리</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G85">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="H85" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="86">
@@ -2330,22 +2499,25 @@
         <v>83</v>
       </c>
       <c r="B86" s="1" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-19T00:00:00.000Z</v>
       </c>
       <c r="C86" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D86" t="str">
-        <v>TP-4401</v>
+        <v>TP-4405</v>
       </c>
       <c r="E86" t="str">
-        <v>샤프트</v>
+        <v>플랜지</v>
       </c>
       <c r="F86" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H86" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="87">
@@ -2353,22 +2525,22 @@
         <v>84</v>
       </c>
       <c r="B87" s="1" t="d">
-        <v>2026-05-31T00:00:00.000Z</v>
+        <v>2026-05-20T00:00:00.000Z</v>
       </c>
       <c r="C87" t="str">
-        <v>협력사 F</v>
+        <v>협력사 B</v>
       </c>
       <c r="D87" t="str">
-        <v>TP-6601</v>
+        <v>TP-2202</v>
       </c>
       <c r="E87" t="str">
-        <v>가이드</v>
+        <v>커버</v>
       </c>
       <c r="F87" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>검사성적서 미첨부</v>
       </c>
       <c r="G87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2376,22 +2548,25 @@
         <v>85</v>
       </c>
       <c r="B88" s="1" t="d">
-        <v>2026-06-03T00:00:00.000Z</v>
+        <v>2026-05-20T00:00:00.000Z</v>
       </c>
       <c r="C88" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D88" t="str">
-        <v>TP-3301</v>
+        <v>TP-3302</v>
       </c>
       <c r="E88" t="str">
-        <v>프레임</v>
+        <v>브래킷</v>
       </c>
       <c r="F88" t="str">
-        <v>표면 찍힘</v>
+        <v>탭 나사산 불량</v>
       </c>
       <c r="G88">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H88" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="89">
@@ -2399,22 +2574,25 @@
         <v>86</v>
       </c>
       <c r="B89" s="1" t="d">
-        <v>2026-06-04T00:00:00.000Z</v>
+        <v>2026-05-21T00:00:00.000Z</v>
       </c>
       <c r="C89" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D89" t="str">
-        <v>TP-1103</v>
+        <v>TP-3302</v>
       </c>
       <c r="E89" t="str">
-        <v>커버</v>
+        <v>브래킷</v>
       </c>
       <c r="F89" t="str">
-        <v>표면 찍힘</v>
+        <v>용접 기공 다수</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H89" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="90">
@@ -2422,22 +2600,22 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="d">
-        <v>2026-06-08T00:00:00.000Z</v>
+        <v>2026-05-23T00:00:00.000Z</v>
       </c>
       <c r="C90" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D90" t="str">
-        <v>TP-4403</v>
+        <v>TP-4405</v>
       </c>
       <c r="E90" t="str">
-        <v>하우징</v>
+        <v>플랜지</v>
       </c>
       <c r="F90" t="str">
-        <v>보관 중 녹 발생</v>
+        <v>오조립(방향 반대)</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -2445,22 +2623,25 @@
         <v>88</v>
       </c>
       <c r="B91" s="1" t="d">
-        <v>2026-06-10T00:00:00.000Z</v>
+        <v>2026-05-29T00:00:00.000Z</v>
       </c>
       <c r="C91" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D91" t="str">
-        <v>TP-4401</v>
+        <v>TP-4405</v>
       </c>
       <c r="E91" t="str">
-        <v>샤프트</v>
+        <v>플랜지</v>
       </c>
       <c r="F91" t="str">
-        <v>스크래치 다수</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H91" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="92">
@@ -2468,22 +2649,25 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="d">
-        <v>2026-06-10T00:00:00.000Z</v>
+        <v>2026-05-30T00:00:00.000Z</v>
       </c>
       <c r="C92" t="str">
-        <v>협력사 E</v>
+        <v>협력사 C</v>
       </c>
       <c r="D92" t="str">
-        <v>TP-5502</v>
+        <v>TP-3301</v>
       </c>
       <c r="E92" t="str">
-        <v>호스 ASSY</v>
+        <v>프레임</v>
       </c>
       <c r="F92" t="str">
-        <v>너트 풀림</v>
+        <v>체결면 단차 발생</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H92" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="93">
@@ -2491,22 +2675,25 @@
         <v>90</v>
       </c>
       <c r="B93" s="1" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C93" t="str">
-        <v>협력사 D</v>
+        <v>협력사 A</v>
       </c>
       <c r="D93" t="str">
-        <v>TP-4403</v>
+        <v>TP-1103</v>
       </c>
       <c r="E93" t="str">
-        <v>하우징</v>
+        <v>커버</v>
       </c>
       <c r="F93" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>이종품 혼입 (타 품번 2개 섞임)</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H93" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="94">
@@ -2514,22 +2701,22 @@
         <v>91</v>
       </c>
       <c r="B94" s="1" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-05-31T00:00:00.000Z</v>
       </c>
       <c r="C94" t="str">
-        <v>협력사 D</v>
+        <v>협력사 C</v>
       </c>
       <c r="D94" t="str">
-        <v>TP-4405</v>
+        <v>TP-3301</v>
       </c>
       <c r="E94" t="str">
-        <v>플랜지</v>
+        <v>프레임</v>
       </c>
       <c r="F94" t="str">
-        <v>가공 치수 규격 미달(외경)</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2537,22 +2724,25 @@
         <v>92</v>
       </c>
       <c r="B95" s="1" t="d">
-        <v>2026-06-15T00:00:00.000Z</v>
+        <v>2026-06-03T00:00:00.000Z</v>
       </c>
       <c r="C95" t="str">
-        <v>협력사 E</v>
+        <v>협력사 C</v>
       </c>
       <c r="D95" t="str">
-        <v>TP-5502</v>
+        <v>TP-3303</v>
       </c>
       <c r="E95" t="str">
-        <v>호스 ASSY</v>
+        <v>서포트</v>
       </c>
       <c r="F95" t="str">
-        <v>유압 파이프 연결부 누유</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H95" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="96">
@@ -2560,22 +2750,25 @@
         <v>93</v>
       </c>
       <c r="B96" s="1" t="d">
-        <v>2026-06-23T00:00:00.000Z</v>
+        <v>2026-06-04T00:00:00.000Z</v>
       </c>
       <c r="C96" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D96" t="str">
-        <v>TP-2201</v>
+        <v>TP-4405</v>
       </c>
       <c r="E96" t="str">
-        <v>탱크</v>
+        <v>플랜지</v>
       </c>
       <c r="F96" t="str">
-        <v>도장 흐름 발생</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H96" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="97">
@@ -2583,7 +2776,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="1" t="d">
-        <v>2026-06-25T00:00:00.000Z</v>
+        <v>2026-06-05T00:00:00.000Z</v>
       </c>
       <c r="C97" t="str">
         <v>협력사 B</v>
@@ -2595,10 +2788,13 @@
         <v>도어 판넬</v>
       </c>
       <c r="F97" t="str">
-        <v>도장 박리</v>
+        <v>체결면 단차 발생</v>
       </c>
       <c r="G97">
         <v>2</v>
+      </c>
+      <c r="H97" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="98">
@@ -2606,22 +2802,25 @@
         <v>95</v>
       </c>
       <c r="B98" s="1" t="d">
-        <v>2026-06-29T00:00:00.000Z</v>
+        <v>2026-06-11T00:00:00.000Z</v>
       </c>
       <c r="C98" t="str">
         <v>협력사 B</v>
       </c>
       <c r="D98" t="str">
-        <v>TP-2201</v>
+        <v>TP-2203</v>
       </c>
       <c r="E98" t="str">
-        <v>탱크</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F98" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>체결면 단차 발생</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H98" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="99">
@@ -2629,22 +2828,25 @@
         <v>96</v>
       </c>
       <c r="B99" s="1" t="d">
-        <v>2026-07-01T00:00:00.000Z</v>
+        <v>2026-06-13T00:00:00.000Z</v>
       </c>
       <c r="C99" t="str">
         <v>협력사 B</v>
       </c>
       <c r="D99" t="str">
-        <v>TP-2201</v>
+        <v>TP-2203</v>
       </c>
       <c r="E99" t="str">
-        <v>탱크</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F99" t="str">
-        <v>도장면 기포</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H99" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="100">
@@ -2652,22 +2854,25 @@
         <v>97</v>
       </c>
       <c r="B100" s="1" t="d">
-        <v>2026-07-04T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C100" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D100" t="str">
-        <v>TP-1104</v>
+        <v>TP-3302</v>
       </c>
       <c r="E100" t="str">
-        <v>핀</v>
+        <v>브래킷</v>
       </c>
       <c r="F100" t="str">
         <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H100" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="101">
@@ -2675,22 +2880,22 @@
         <v>98</v>
       </c>
       <c r="B101" s="1" t="d">
-        <v>2026-07-04T00:00:00.000Z</v>
+        <v>2026-06-15T00:00:00.000Z</v>
       </c>
       <c r="C101" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D101" t="str">
-        <v>TP-2201</v>
+        <v>TP-4405</v>
       </c>
       <c r="E101" t="str">
-        <v>탱크</v>
+        <v>플랜지</v>
       </c>
       <c r="F101" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -2698,7 +2903,7 @@
         <v>99</v>
       </c>
       <c r="B102" s="1" t="d">
-        <v>2026-07-07T00:00:00.000Z</v>
+        <v>2026-06-19T00:00:00.000Z</v>
       </c>
       <c r="C102" t="str">
         <v>협력사 E</v>
@@ -2710,10 +2915,10 @@
         <v>호스 ASSY</v>
       </c>
       <c r="F102" t="str">
-        <v>이물 부착</v>
+        <v>기밀 시험 리크 발생</v>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2721,22 +2926,25 @@
         <v>100</v>
       </c>
       <c r="B103" s="1" t="d">
-        <v>2026-07-08T00:00:00.000Z</v>
+        <v>2026-06-29T00:00:00.000Z</v>
       </c>
       <c r="C103" t="str">
         <v>협력사 A</v>
       </c>
       <c r="D103" t="str">
-        <v>TP-1104</v>
+        <v>TP-1103</v>
       </c>
       <c r="E103" t="str">
-        <v>핀</v>
+        <v>커버</v>
       </c>
       <c r="F103" t="str">
-        <v>이종 볼트 혼용</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H103" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="104">
@@ -2744,22 +2952,22 @@
         <v>101</v>
       </c>
       <c r="B104" s="1" t="d">
-        <v>2026-07-08T00:00:00.000Z</v>
+        <v>2026-07-04T00:00:00.000Z</v>
       </c>
       <c r="C104" t="str">
-        <v>협력사 A</v>
+        <v>협력사 D</v>
       </c>
       <c r="D104" t="str">
-        <v>TP-1102</v>
+        <v>TP-4405</v>
       </c>
       <c r="E104" t="str">
-        <v>브래킷 ASSY</v>
+        <v>플랜지</v>
       </c>
       <c r="F104" t="str">
-        <v>라벨 오류로 품번 상이</v>
+        <v>스크래치 다수</v>
       </c>
       <c r="G104">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -2767,22 +2975,22 @@
         <v>102</v>
       </c>
       <c r="B105" s="1" t="d">
-        <v>2026-07-14T00:00:00.000Z</v>
+        <v>2026-07-06T00:00:00.000Z</v>
       </c>
       <c r="C105" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D105" t="str">
-        <v>TP-5503</v>
+        <v>TP-2203</v>
       </c>
       <c r="E105" t="str">
-        <v>밸브 블록</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F105" t="str">
-        <v>피팅부 오일 샘</v>
+        <v>보관 중 녹 발생</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -2790,22 +2998,25 @@
         <v>103</v>
       </c>
       <c r="B106" s="1" t="d">
-        <v>2026-07-14T00:00:00.000Z</v>
+        <v>2026-07-08T00:00:00.000Z</v>
       </c>
       <c r="C106" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D106" t="str">
-        <v>TP-5502</v>
+        <v>TP-1102</v>
       </c>
       <c r="E106" t="str">
-        <v>호스 ASSY</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F106" t="str">
-        <v>납품 수량 부족</v>
+        <v>와셔 누락</v>
       </c>
       <c r="G106">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="H106" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="107">
@@ -2813,22 +3024,22 @@
         <v>104</v>
       </c>
       <c r="B107" s="1" t="d">
-        <v>2026-07-17T00:00:00.000Z</v>
+        <v>2026-07-12T00:00:00.000Z</v>
       </c>
       <c r="C107" t="str">
-        <v>협력사 D</v>
+        <v>협력사 C</v>
       </c>
       <c r="D107" t="str">
-        <v>TP-4402</v>
+        <v>TP-3303</v>
       </c>
       <c r="E107" t="str">
-        <v>부싱</v>
+        <v>서포트</v>
       </c>
       <c r="F107" t="str">
-        <v>가공면 burr 잔존</v>
+        <v>용접 기공 다수</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -2836,22 +3047,25 @@
         <v>105</v>
       </c>
       <c r="B108" s="1" t="d">
-        <v>2026-07-22T00:00:00.000Z</v>
+        <v>2026-07-13T00:00:00.000Z</v>
       </c>
       <c r="C108" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D108" t="str">
-        <v>TP-4402</v>
+        <v>TP-4401</v>
       </c>
       <c r="E108" t="str">
-        <v>부싱</v>
+        <v>샤프트</v>
       </c>
       <c r="F108" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>탭 나사산 불량</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H108" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="109">
@@ -2859,22 +3073,22 @@
         <v>106</v>
       </c>
       <c r="B109" s="1" t="d">
-        <v>2026-07-23T00:00:00.000Z</v>
+        <v>2026-07-14T00:00:00.000Z</v>
       </c>
       <c r="C109" t="str">
-        <v>협력사 D</v>
+        <v>협력사 E</v>
       </c>
       <c r="D109" t="str">
-        <v>TP-4403</v>
+        <v>TP-5502</v>
       </c>
       <c r="E109" t="str">
-        <v>하우징</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F109" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>원인 확인 중</v>
       </c>
       <c r="G109">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110">
@@ -2882,22 +3096,22 @@
         <v>107</v>
       </c>
       <c r="B110" s="1" t="d">
-        <v>2026-07-23T00:00:00.000Z</v>
+        <v>2026-07-17T00:00:00.000Z</v>
       </c>
       <c r="C110" t="str">
-        <v>협력사 E</v>
+        <v>협력사 C</v>
       </c>
       <c r="D110" t="str">
-        <v>TP-5501</v>
+        <v>TP-3303</v>
       </c>
       <c r="E110" t="str">
-        <v>유압 파이프</v>
+        <v>서포트</v>
       </c>
       <c r="F110" t="str">
-        <v>오조립(방향 반대)</v>
+        <v>언더컷 발생</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -2905,19 +3119,19 @@
         <v>108</v>
       </c>
       <c r="B111" s="1" t="d">
-        <v>2026-08-03T00:00:00.000Z</v>
+        <v>2026-07-18T00:00:00.000Z</v>
       </c>
       <c r="C111" t="str">
-        <v>협력사 D</v>
+        <v>협력사 E</v>
       </c>
       <c r="D111" t="str">
-        <v>TP-4403</v>
+        <v>TP-5501</v>
       </c>
       <c r="E111" t="str">
-        <v>하우징</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F111" t="str">
-        <v>가공면 burr 잔존</v>
+        <v>피팅부 오일 샘</v>
       </c>
       <c r="G111">
         <v>6</v>
@@ -2928,22 +3142,22 @@
         <v>109</v>
       </c>
       <c r="B112" s="1" t="d">
-        <v>2026-08-04T00:00:00.000Z</v>
+        <v>2026-07-23T00:00:00.000Z</v>
       </c>
       <c r="C112" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D112" t="str">
-        <v>TP-3301</v>
+        <v>TP-4403</v>
       </c>
       <c r="E112" t="str">
-        <v>프레임</v>
+        <v>하우징</v>
       </c>
       <c r="F112" t="str">
-        <v>용접부 균열 발생</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -2951,22 +3165,25 @@
         <v>110</v>
       </c>
       <c r="B113" s="1" t="d">
-        <v>2026-08-11T00:00:00.000Z</v>
+        <v>2026-07-24T00:00:00.000Z</v>
       </c>
       <c r="C113" t="str">
-        <v>협력사 D</v>
+        <v>협력사 B</v>
       </c>
       <c r="D113" t="str">
-        <v>TP-4405</v>
+        <v>TP-2202</v>
       </c>
       <c r="E113" t="str">
-        <v>플랜지</v>
+        <v>커버</v>
       </c>
       <c r="F113" t="str">
-        <v>평면도 불량</v>
+        <v>오조립(방향 반대)</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="H113" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="114">
@@ -2974,22 +3191,25 @@
         <v>111</v>
       </c>
       <c r="B114" s="1" t="d">
-        <v>2026-08-13T00:00:00.000Z</v>
+        <v>2026-07-26T00:00:00.000Z</v>
       </c>
       <c r="C114" t="str">
-        <v>협력사 A</v>
+        <v>협력사 F</v>
       </c>
       <c r="D114" t="str">
-        <v>TP-1101</v>
+        <v>TP-6602</v>
       </c>
       <c r="E114" t="str">
-        <v>브래킷</v>
+        <v>스페이서</v>
       </c>
       <c r="F114" t="str">
-        <v>오조립(방향 반대)</v>
+        <v>탭 나사산 불량</v>
       </c>
       <c r="G114">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H114" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="115">
@@ -2997,22 +3217,25 @@
         <v>112</v>
       </c>
       <c r="B115" s="1" t="d">
-        <v>2026-08-13T00:00:00.000Z</v>
+        <v>2026-08-01T00:00:00.000Z</v>
       </c>
       <c r="C115" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D115" t="str">
-        <v>TP-2201</v>
+        <v>TP-3303</v>
       </c>
       <c r="E115" t="str">
-        <v>탱크</v>
+        <v>서포트</v>
       </c>
       <c r="F115" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>조립 시 상대 부품과 간섭</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H115" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="116">
@@ -3020,22 +3243,22 @@
         <v>113</v>
       </c>
       <c r="B116" s="1" t="d">
-        <v>2026-08-14T00:00:00.000Z</v>
+        <v>2026-08-04T00:00:00.000Z</v>
       </c>
       <c r="C116" t="str">
-        <v>협력사 E</v>
+        <v>협력사 C</v>
       </c>
       <c r="D116" t="str">
-        <v>TP-5501</v>
+        <v>TP-3301</v>
       </c>
       <c r="E116" t="str">
-        <v>유압 파이프</v>
+        <v>프레임</v>
       </c>
       <c r="F116" t="str">
-        <v>유압 파이프 연결부 누유</v>
+        <v>용접부 균열 발생</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3043,22 +3266,22 @@
         <v>114</v>
       </c>
       <c r="B117" s="1" t="d">
-        <v>2026-08-16T00:00:00.000Z</v>
+        <v>2026-08-06T00:00:00.000Z</v>
       </c>
       <c r="C117" t="str">
-        <v>협력사 B</v>
+        <v>협력사 A</v>
       </c>
       <c r="D117" t="str">
-        <v>TP-2201</v>
+        <v>TP-1104</v>
       </c>
       <c r="E117" t="str">
-        <v>탱크</v>
+        <v>핀</v>
       </c>
       <c r="F117" t="str">
-        <v>표면 찍힘</v>
+        <v>라벨 오류로 품번 상이</v>
       </c>
       <c r="G117">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3066,22 +3289,22 @@
         <v>115</v>
       </c>
       <c r="B118" s="1" t="d">
-        <v>2026-08-19T00:00:00.000Z</v>
+        <v>2026-08-06T00:00:00.000Z</v>
       </c>
       <c r="C118" t="str">
-        <v>협력사 B</v>
+        <v>협력사 E</v>
       </c>
       <c r="D118" t="str">
-        <v>TP-2202</v>
+        <v>TP-5503</v>
       </c>
       <c r="E118" t="str">
-        <v>커버</v>
+        <v>밸브 블록</v>
       </c>
       <c r="F118" t="str">
-        <v>도장면 기포</v>
+        <v>너트 풀림</v>
       </c>
       <c r="G118">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3089,22 +3312,25 @@
         <v>116</v>
       </c>
       <c r="B119" s="1" t="d">
-        <v>2026-08-21T00:00:00.000Z</v>
+        <v>2026-08-07T00:00:00.000Z</v>
       </c>
       <c r="C119" t="str">
-        <v>협력사 C</v>
+        <v>협력사 B</v>
       </c>
       <c r="D119" t="str">
-        <v>TP-3301</v>
+        <v>TP-2202</v>
       </c>
       <c r="E119" t="str">
-        <v>프레임</v>
+        <v>커버</v>
       </c>
       <c r="F119" t="str">
-        <v>용접 비드 끝단 크랙</v>
+        <v>작동 시 소음 발생</v>
       </c>
       <c r="G119">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H119" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="120">
@@ -3112,22 +3338,25 @@
         <v>117</v>
       </c>
       <c r="B120" s="1" t="d">
-        <v>2026-08-23T00:00:00.000Z</v>
+        <v>2026-08-11T00:00:00.000Z</v>
       </c>
       <c r="C120" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D120" t="str">
-        <v>TP-3303</v>
+        <v>TP-4401</v>
       </c>
       <c r="E120" t="str">
-        <v>서포트</v>
+        <v>샤프트</v>
       </c>
       <c r="F120" t="str">
-        <v>용접 기공 다수</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G120">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H120" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="121">
@@ -3135,22 +3364,22 @@
         <v>118</v>
       </c>
       <c r="B121" s="1" t="d">
-        <v>2026-08-24T00:00:00.000Z</v>
+        <v>2026-08-14T00:00:00.000Z</v>
       </c>
       <c r="C121" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D121" t="str">
-        <v>TP-3301</v>
+        <v>TP-4401</v>
       </c>
       <c r="E121" t="str">
-        <v>프레임</v>
+        <v>샤프트</v>
       </c>
       <c r="F121" t="str">
-        <v>스패터 과다 부착</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G121">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3158,22 +3387,25 @@
         <v>119</v>
       </c>
       <c r="B122" s="1" t="d">
-        <v>2026-08-26T00:00:00.000Z</v>
+        <v>2026-08-15T00:00:00.000Z</v>
       </c>
       <c r="C122" t="str">
-        <v>협력사 D</v>
+        <v>협력사 C</v>
       </c>
       <c r="D122" t="str">
-        <v>TP-4405</v>
+        <v>TP-3303</v>
       </c>
       <c r="E122" t="str">
-        <v>플랜지</v>
+        <v>서포트</v>
       </c>
       <c r="F122" t="str">
-        <v>탭 나사산 불량</v>
+        <v>용접 기공 다수</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H122" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="123">
@@ -3181,22 +3413,22 @@
         <v>120</v>
       </c>
       <c r="B123" s="1" t="d">
-        <v>2026-09-02T00:00:00.000Z</v>
+        <v>2026-08-17T00:00:00.000Z</v>
       </c>
       <c r="C123" t="str">
-        <v>협력사 C</v>
+        <v>협력사 A</v>
       </c>
       <c r="D123" t="str">
-        <v>TP-3303</v>
+        <v>TP-1103</v>
       </c>
       <c r="E123" t="str">
-        <v>서포트</v>
+        <v>커버</v>
       </c>
       <c r="F123" t="str">
-        <v>브래킷 용접부 갈라짐</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G123">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -3204,22 +3436,25 @@
         <v>121</v>
       </c>
       <c r="B124" s="1" t="d">
-        <v>2026-09-04T00:00:00.000Z</v>
+        <v>2026-08-19T00:00:00.000Z</v>
       </c>
       <c r="C124" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D124" t="str">
-        <v>TP-1103</v>
+        <v>TP-3301</v>
       </c>
       <c r="E124" t="str">
-        <v>커버</v>
+        <v>프레임</v>
       </c>
       <c r="F124" t="str">
-        <v>사양 상이 부품 혼입</v>
+        <v>브래킷 정렬 틀어짐</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H124" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="125">
@@ -3227,22 +3462,25 @@
         <v>122</v>
       </c>
       <c r="B125" s="1" t="d">
-        <v>2026-09-04T00:00:00.000Z</v>
+        <v>2026-08-21T00:00:00.000Z</v>
       </c>
       <c r="C125" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D125" t="str">
-        <v>TP-1104</v>
+        <v>TP-3301</v>
       </c>
       <c r="E125" t="str">
-        <v>핀</v>
+        <v>프레임</v>
       </c>
       <c r="F125" t="str">
-        <v>운송 중 변형(휨)</v>
+        <v>용접 비드 끝단 크랙</v>
       </c>
       <c r="G125">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H125" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="126">
@@ -3250,22 +3488,22 @@
         <v>123</v>
       </c>
       <c r="B126" s="1" t="d">
-        <v>2026-09-05T00:00:00.000Z</v>
+        <v>2026-08-26T00:00:00.000Z</v>
       </c>
       <c r="C126" t="str">
-        <v>협력사 A</v>
+        <v>협력사 D</v>
       </c>
       <c r="D126" t="str">
-        <v>TP-1104</v>
+        <v>TP-4405</v>
       </c>
       <c r="E126" t="str">
-        <v>핀</v>
+        <v>플랜지</v>
       </c>
       <c r="F126" t="str">
-        <v>사양 상이 부품 혼입</v>
+        <v>탭 나사산 불량</v>
       </c>
       <c r="G126">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3273,22 +3511,25 @@
         <v>124</v>
       </c>
       <c r="B127" s="1" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-08-29T00:00:00.000Z</v>
       </c>
       <c r="C127" t="str">
         <v>협력사 A</v>
       </c>
       <c r="D127" t="str">
-        <v>TP-1101</v>
+        <v>TP-1104</v>
       </c>
       <c r="E127" t="str">
-        <v>브래킷</v>
+        <v>핀</v>
       </c>
       <c r="F127" t="str">
-        <v>라벨 오류로 품번 상이</v>
+        <v>너트 풀림</v>
       </c>
       <c r="G127">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H127" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="128">
@@ -3296,22 +3537,22 @@
         <v>125</v>
       </c>
       <c r="B128" s="1" t="d">
-        <v>2026-09-07T00:00:00.000Z</v>
+        <v>2026-09-02T00:00:00.000Z</v>
       </c>
       <c r="C128" t="str">
-        <v>협력사 A</v>
+        <v>협력사 C</v>
       </c>
       <c r="D128" t="str">
-        <v>TP-1104</v>
+        <v>TP-3303</v>
       </c>
       <c r="E128" t="str">
-        <v>핀</v>
+        <v>서포트</v>
       </c>
       <c r="F128" t="str">
-        <v>가공면 burr 잔존</v>
+        <v>브래킷 용접부 갈라짐</v>
       </c>
       <c r="G128">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3319,22 +3560,25 @@
         <v>126</v>
       </c>
       <c r="B129" s="1" t="d">
-        <v>2026-09-08T00:00:00.000Z</v>
+        <v>2026-09-04T00:00:00.000Z</v>
       </c>
       <c r="C129" t="str">
-        <v>협력사 B</v>
+        <v>협력사 A</v>
       </c>
       <c r="D129" t="str">
-        <v>TP-2201</v>
+        <v>TP-1103</v>
       </c>
       <c r="E129" t="str">
-        <v>탱크</v>
+        <v>커버</v>
       </c>
       <c r="F129" t="str">
-        <v>도장 흐름 발생</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G129">
         <v>1</v>
+      </c>
+      <c r="H129" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="130">
@@ -3342,22 +3586,25 @@
         <v>127</v>
       </c>
       <c r="B130" s="1" t="d">
-        <v>2026-09-09T00:00:00.000Z</v>
+        <v>2026-09-04T00:00:00.000Z</v>
       </c>
       <c r="C130" t="str">
-        <v>협력사 F</v>
+        <v>협력사 E</v>
       </c>
       <c r="D130" t="str">
-        <v>TP-6601</v>
+        <v>TP-5501</v>
       </c>
       <c r="E130" t="str">
-        <v>가이드</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F130" t="str">
-        <v>원인 확인 중</v>
+        <v>기밀 시험 리크 발생</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H130" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="131">
@@ -3365,19 +3612,19 @@
         <v>128</v>
       </c>
       <c r="B131" s="1" t="d">
-        <v>2026-09-16T00:00:00.000Z</v>
+        <v>2026-09-05T00:00:00.000Z</v>
       </c>
       <c r="C131" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D131" t="str">
-        <v>TP-3302</v>
+        <v>TP-5502</v>
       </c>
       <c r="E131" t="str">
-        <v>브래킷</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F131" t="str">
-        <v>탭 나사산 불량</v>
+        <v>볼트 체결 토크 부족</v>
       </c>
       <c r="G131">
         <v>3</v>
@@ -3388,22 +3635,25 @@
         <v>129</v>
       </c>
       <c r="B132" s="1" t="d">
-        <v>2026-09-17T00:00:00.000Z</v>
+        <v>2026-09-06T00:00:00.000Z</v>
       </c>
       <c r="C132" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D132" t="str">
-        <v>TP-3301</v>
+        <v>TP-5501</v>
       </c>
       <c r="E132" t="str">
-        <v>프레임</v>
+        <v>유압 파이프</v>
       </c>
       <c r="F132" t="str">
-        <v>용접 후 균열(열영향부)</v>
+        <v>너트 풀림</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H132" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="133">
@@ -3411,22 +3661,25 @@
         <v>130</v>
       </c>
       <c r="B133" s="1" t="d">
-        <v>2026-09-20T00:00:00.000Z</v>
+        <v>2026-09-07T00:00:00.000Z</v>
       </c>
       <c r="C133" t="str">
-        <v>협력사 E</v>
+        <v>협력사 A</v>
       </c>
       <c r="D133" t="str">
-        <v>TP-5503</v>
+        <v>TP-1101</v>
       </c>
       <c r="E133" t="str">
-        <v>밸브 블록</v>
+        <v>브래킷</v>
       </c>
       <c r="F133" t="str">
-        <v>스크래치 다수</v>
+        <v>와셔 누락</v>
       </c>
       <c r="G133">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H133" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="134">
@@ -3434,22 +3687,22 @@
         <v>131</v>
       </c>
       <c r="B134" s="1" t="d">
-        <v>2026-09-21T00:00:00.000Z</v>
+        <v>2026-09-08T00:00:00.000Z</v>
       </c>
       <c r="C134" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D134" t="str">
-        <v>TP-5503</v>
+        <v>TP-2201</v>
       </c>
       <c r="E134" t="str">
-        <v>밸브 블록</v>
+        <v>탱크</v>
       </c>
       <c r="F134" t="str">
-        <v>기밀 시험 리크 발생</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G134">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3457,22 +3710,22 @@
         <v>132</v>
       </c>
       <c r="B135" s="1" t="d">
-        <v>2026-09-22T00:00:00.000Z</v>
+        <v>2026-09-09T00:00:00.000Z</v>
       </c>
       <c r="C135" t="str">
-        <v>협력사 B</v>
+        <v>협력사 F</v>
       </c>
       <c r="D135" t="str">
-        <v>TP-2202</v>
+        <v>TP-6601</v>
       </c>
       <c r="E135" t="str">
-        <v>커버</v>
+        <v>가이드</v>
       </c>
       <c r="F135" t="str">
-        <v>스크래치 다수</v>
+        <v>납품 서류 확인 필요</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3480,22 +3733,25 @@
         <v>133</v>
       </c>
       <c r="B136" s="1" t="d">
-        <v>2026-09-22T00:00:00.000Z</v>
+        <v>2026-09-12T00:00:00.000Z</v>
       </c>
       <c r="C136" t="str">
-        <v>협력사 B</v>
+        <v>협력사 D</v>
       </c>
       <c r="D136" t="str">
-        <v>TP-2201</v>
+        <v>TP-4401</v>
       </c>
       <c r="E136" t="str">
-        <v>탱크</v>
+        <v>샤프트</v>
       </c>
       <c r="F136" t="str">
-        <v>미도장 부위 있음</v>
+        <v>평면도 불량</v>
       </c>
       <c r="G136">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H136" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="137">
@@ -3503,7 +3759,7 @@
         <v>134</v>
       </c>
       <c r="B137" s="1" t="d">
-        <v>2026-09-22T00:00:00.000Z</v>
+        <v>2026-09-16T00:00:00.000Z</v>
       </c>
       <c r="C137" t="str">
         <v>협력사 C</v>
@@ -3515,10 +3771,10 @@
         <v>프레임</v>
       </c>
       <c r="F137" t="str">
-        <v>이물 부착</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
@@ -3526,22 +3782,25 @@
         <v>135</v>
       </c>
       <c r="B138" s="1" t="d">
-        <v>2026-09-22T00:00:00.000Z</v>
+        <v>2026-09-17T00:00:00.000Z</v>
       </c>
       <c r="C138" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D138" t="str">
-        <v>TP-3302</v>
+        <v>TP-3301</v>
       </c>
       <c r="E138" t="str">
-        <v>브래킷</v>
+        <v>프레임</v>
       </c>
       <c r="F138" t="str">
-        <v>스패터 과다 부착</v>
+        <v>용접 후 균열(열영향부)</v>
       </c>
       <c r="G138">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="H138" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="139">
@@ -3549,22 +3808,22 @@
         <v>136</v>
       </c>
       <c r="B139" s="1" t="d">
-        <v>2026-09-23T00:00:00.000Z</v>
+        <v>2026-09-19T00:00:00.000Z</v>
       </c>
       <c r="C139" t="str">
-        <v>협력사 A</v>
+        <v>협력사 B</v>
       </c>
       <c r="D139" t="str">
-        <v>TP-1102</v>
+        <v>TP-2202</v>
       </c>
       <c r="E139" t="str">
-        <v>브래킷 ASSY</v>
+        <v>커버</v>
       </c>
       <c r="F139" t="str">
-        <v>이종품 혼입 (타 품번 2개 섞임)</v>
+        <v>도장 흐름 발생</v>
       </c>
       <c r="G139">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -3572,7 +3831,7 @@
         <v>137</v>
       </c>
       <c r="B140" s="1" t="d">
-        <v>2026-09-24T00:00:00.000Z</v>
+        <v>2026-09-20T00:00:00.000Z</v>
       </c>
       <c r="C140" t="str">
         <v>협력사 D</v>
@@ -3584,10 +3843,13 @@
         <v>플랜지</v>
       </c>
       <c r="F140" t="str">
-        <v>평면도 불량</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H140" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="141">
@@ -3595,22 +3857,25 @@
         <v>138</v>
       </c>
       <c r="B141" s="1" t="d">
-        <v>2026-09-26T00:00:00.000Z</v>
+        <v>2026-09-22T00:00:00.000Z</v>
       </c>
       <c r="C141" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D141" t="str">
-        <v>TP-5502</v>
+        <v>TP-2202</v>
       </c>
       <c r="E141" t="str">
-        <v>호스 ASSY</v>
+        <v>커버</v>
       </c>
       <c r="F141" t="str">
-        <v>오조립(방향 반대)</v>
+        <v>브래킷 정렬 틀어짐</v>
       </c>
       <c r="G141">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H141" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="142">
@@ -3618,22 +3883,25 @@
         <v>139</v>
       </c>
       <c r="B142" s="1" t="d">
-        <v>2026-09-28T00:00:00.000Z</v>
+        <v>2026-09-23T00:00:00.000Z</v>
       </c>
       <c r="C142" t="str">
-        <v>협력사 B</v>
+        <v>협력사 A</v>
       </c>
       <c r="D142" t="str">
-        <v>TP-2203</v>
+        <v>TP-1102</v>
       </c>
       <c r="E142" t="str">
-        <v>도어 판넬</v>
+        <v>브래킷 ASSY</v>
       </c>
       <c r="F142" t="str">
-        <v>도막 두께 부족</v>
+        <v>이종품 혼입 (타 품번 2개 섞임)</v>
       </c>
       <c r="G142">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="H142" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="143">
@@ -3641,22 +3909,25 @@
         <v>140</v>
       </c>
       <c r="B143" s="1" t="d">
-        <v>2026-09-29T00:00:00.000Z</v>
+        <v>2026-09-23T00:00:00.000Z</v>
       </c>
       <c r="C143" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D143" t="str">
-        <v>TP-3301</v>
+        <v>TP-4401</v>
       </c>
       <c r="E143" t="str">
-        <v>프레임</v>
+        <v>샤프트</v>
       </c>
       <c r="F143" t="str">
-        <v>용접부 균열 발생</v>
+        <v>홀 위치 치수 공차 초과</v>
       </c>
       <c r="G143">
         <v>2</v>
+      </c>
+      <c r="H143" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="144">
@@ -3664,22 +3935,25 @@
         <v>141</v>
       </c>
       <c r="B144" s="1" t="d">
-        <v>2026-10-03T00:00:00.000Z</v>
+        <v>2026-09-25T00:00:00.000Z</v>
       </c>
       <c r="C144" t="str">
-        <v>협력사 C</v>
+        <v>협력사 A</v>
       </c>
       <c r="D144" t="str">
-        <v>TP-3301</v>
+        <v>TP-1104</v>
       </c>
       <c r="E144" t="str">
-        <v>프레임</v>
+        <v>핀</v>
       </c>
       <c r="F144" t="str">
-        <v>홀 위치 치수 공차 초과</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G144">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H144" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="145">
@@ -3687,7 +3961,7 @@
         <v>142</v>
       </c>
       <c r="B145" s="1" t="d">
-        <v>2026-10-04T00:00:00.000Z</v>
+        <v>2026-09-26T00:00:00.000Z</v>
       </c>
       <c r="C145" t="str">
         <v>협력사 E</v>
@@ -3699,10 +3973,13 @@
         <v>호스 ASSY</v>
       </c>
       <c r="F145" t="str">
-        <v>기밀 시험 리크 발생</v>
+        <v>피팅부 오일 샘</v>
       </c>
       <c r="G145">
         <v>3</v>
+      </c>
+      <c r="H145" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="146">
@@ -3710,22 +3987,22 @@
         <v>143</v>
       </c>
       <c r="B146" s="1" t="d">
-        <v>2026-10-06T00:00:00.000Z</v>
+        <v>2026-09-29T00:00:00.000Z</v>
       </c>
       <c r="C146" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D146" t="str">
-        <v>TP-2203</v>
+        <v>TP-3301</v>
       </c>
       <c r="E146" t="str">
-        <v>도어 판넬</v>
+        <v>프레임</v>
       </c>
       <c r="F146" t="str">
-        <v>도막 두께 부족</v>
+        <v>용접부 균열 발생</v>
       </c>
       <c r="G146">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -3733,22 +4010,25 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-02T00:00:00.000Z</v>
       </c>
       <c r="C147" t="str">
-        <v>협력사 C</v>
+        <v>협력사 A</v>
       </c>
       <c r="D147" t="str">
-        <v>TP-3303</v>
+        <v>TP-1104</v>
       </c>
       <c r="E147" t="str">
-        <v>서포트</v>
+        <v>핀</v>
       </c>
       <c r="F147" t="str">
-        <v>용접 비드 끝단 크랙</v>
+        <v>부품 미장착 상태로 입고</v>
       </c>
       <c r="G147">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H147" t="str">
+        <v>임시 보수</v>
       </c>
     </row>
     <row r="148">
@@ -3756,22 +4036,25 @@
         <v>145</v>
       </c>
       <c r="B148" s="1" t="d">
-        <v>2026-10-08T00:00:00.000Z</v>
+        <v>2026-10-02T00:00:00.000Z</v>
       </c>
       <c r="C148" t="str">
-        <v>협력사 E</v>
+        <v>협력사 B</v>
       </c>
       <c r="D148" t="str">
-        <v>TP-5503</v>
+        <v>TP-2203</v>
       </c>
       <c r="E148" t="str">
-        <v>밸브 블록</v>
+        <v>도어 판넬</v>
       </c>
       <c r="F148" t="str">
-        <v>유압 파이프 연결부 누유</v>
+        <v>표면 찍힘</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="H148" t="str">
+        <v>특채 사용(현장 승인)</v>
       </c>
     </row>
     <row r="149">
@@ -3779,22 +4062,25 @@
         <v>146</v>
       </c>
       <c r="B149" s="1" t="d">
-        <v>2026-10-11T00:00:00.000Z</v>
+        <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C149" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D149" t="str">
-        <v>TP-2201</v>
+        <v>TP-3303</v>
       </c>
       <c r="E149" t="str">
-        <v>탱크</v>
+        <v>서포트</v>
       </c>
       <c r="F149" t="str">
-        <v>미도장 부위 있음</v>
+        <v>용접 비드 끝단 크랙</v>
       </c>
       <c r="G149">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="H149" t="str">
+        <v>전수 선별</v>
       </c>
     </row>
     <row r="150">
@@ -3802,22 +4088,22 @@
         <v>147</v>
       </c>
       <c r="B150" s="1" t="d">
-        <v>2026-10-11T00:00:00.000Z</v>
+        <v>2026-10-08T00:00:00.000Z</v>
       </c>
       <c r="C150" t="str">
-        <v>협력사 C</v>
+        <v>협력사 D</v>
       </c>
       <c r="D150" t="str">
-        <v>TP-3302</v>
+        <v>TP-4403</v>
       </c>
       <c r="E150" t="str">
-        <v>브래킷</v>
+        <v>하우징</v>
       </c>
       <c r="F150" t="str">
-        <v>각장 부족</v>
+        <v>가공 치수 규격 미달(외경)</v>
       </c>
       <c r="G150">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -3825,22 +4111,25 @@
         <v>148</v>
       </c>
       <c r="B151" s="1" t="d">
-        <v>2026-10-11T00:00:00.000Z</v>
+        <v>2026-10-09T00:00:00.000Z</v>
       </c>
       <c r="C151" t="str">
         <v>협력사 D</v>
       </c>
       <c r="D151" t="str">
-        <v>TP-4405</v>
+        <v>TP-4401</v>
       </c>
       <c r="E151" t="str">
-        <v>플랜지</v>
+        <v>샤프트</v>
       </c>
       <c r="F151" t="str">
-        <v>도금면 부식</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G151">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H151" t="str">
+        <v>재작업 후 재입고</v>
       </c>
     </row>
     <row r="152">
@@ -3848,22 +4137,25 @@
         <v>149</v>
       </c>
       <c r="B152" s="1" t="d">
-        <v>2026-10-12T00:00:00.000Z</v>
+        <v>2026-10-11T00:00:00.000Z</v>
       </c>
       <c r="C152" t="str">
-        <v>협력사 B</v>
+        <v>협력사 C</v>
       </c>
       <c r="D152" t="str">
-        <v>TP-2202</v>
+        <v>TP-3302</v>
       </c>
       <c r="E152" t="str">
-        <v>커버</v>
+        <v>브래킷</v>
       </c>
       <c r="F152" t="str">
-        <v>표면 찍힘</v>
+        <v>브래킷 길이 치수 초과</v>
       </c>
       <c r="G152">
         <v>6</v>
+      </c>
+      <c r="H152" t="str">
+        <v>협력사 반품</v>
       </c>
     </row>
     <row r="153">
@@ -3871,22 +4163,22 @@
         <v>150</v>
       </c>
       <c r="B153" s="1" t="d">
-        <v>2026-10-12T00:00:00.000Z</v>
+        <v>2026-10-14T00:00:00.000Z</v>
       </c>
       <c r="C153" t="str">
         <v>협력사 C</v>
       </c>
       <c r="D153" t="str">
-        <v>TP-3302</v>
+        <v>TP-3301</v>
       </c>
       <c r="E153" t="str">
-        <v>브래킷</v>
+        <v>프레임</v>
       </c>
       <c r="F153" t="str">
-        <v>언더컷 발생</v>
+        <v>브래킷 용접부 갈라짐</v>
       </c>
       <c r="G153">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -3897,27 +4189,27 @@
         <v>2026-10-14T00:00:00.000Z</v>
       </c>
       <c r="C154" t="str">
-        <v>협력사 C</v>
+        <v>협력사 E</v>
       </c>
       <c r="D154" t="str">
-        <v>TP-3301</v>
+        <v>TP-5502</v>
       </c>
       <c r="E154" t="str">
-        <v>프레임</v>
+        <v>호스 ASSY</v>
       </c>
       <c r="F154" t="str">
-        <v>브래킷 용접부 갈라짐</v>
+        <v>볼트 체결 토크 부족</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H154"/>
   </ignoredErrors>
 </worksheet>
 </file>
